--- a/plantilla_catalogo_empleados.xlsx
+++ b/plantilla_catalogo_empleados.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F489"/>
+  <dimension ref="A1:H489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,8 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -507,6 +509,16 @@
           <t>Estatus</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha_Nacimiento (AAAA-MM-DD)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo_Empleado</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -535,6 +547,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -563,6 +577,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -591,6 +607,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -619,6 +637,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -647,6 +667,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -675,6 +697,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -703,6 +727,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -731,6 +757,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -759,6 +787,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -787,6 +817,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -815,6 +847,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -843,6 +877,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -871,6 +907,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -899,6 +937,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -927,6 +967,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -955,6 +997,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -983,6 +1027,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1011,6 +1057,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1039,6 +1087,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1067,6 +1117,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1095,6 +1147,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1123,6 +1177,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1151,6 +1207,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1179,6 +1237,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1207,6 +1267,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1235,6 +1297,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1263,6 +1327,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1291,6 +1357,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1319,6 +1387,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1347,6 +1417,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1375,6 +1447,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1403,6 +1477,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1431,6 +1507,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1459,6 +1537,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1487,6 +1567,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1515,6 +1597,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1543,6 +1627,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1571,6 +1657,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1599,6 +1687,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1627,6 +1717,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1655,6 +1747,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1683,6 +1777,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1711,6 +1807,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1739,6 +1837,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1767,6 +1867,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1795,6 +1897,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1823,6 +1927,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1851,6 +1957,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1879,6 +1987,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1907,6 +2017,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1935,6 +2047,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1963,6 +2077,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1991,6 +2107,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2019,6 +2137,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2047,6 +2167,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2075,6 +2197,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2103,6 +2227,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2131,6 +2257,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2159,6 +2287,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2187,6 +2317,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2215,6 +2347,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2243,6 +2377,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2271,6 +2407,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2299,6 +2437,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2327,6 +2467,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2355,6 +2497,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2383,6 +2527,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2411,6 +2557,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2439,6 +2587,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2467,6 +2617,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2495,6 +2647,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2523,6 +2677,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2551,6 +2707,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2579,6 +2737,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2607,6 +2767,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2635,6 +2797,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2663,6 +2827,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2691,6 +2857,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2719,6 +2887,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2747,6 +2917,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2775,6 +2947,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2803,6 +2977,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2831,6 +3007,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2859,6 +3037,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2887,6 +3067,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2915,6 +3097,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2943,6 +3127,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2971,6 +3157,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2999,6 +3187,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3027,6 +3217,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3055,6 +3247,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3083,6 +3277,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3111,6 +3307,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3139,6 +3337,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3167,6 +3367,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3195,6 +3397,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3223,6 +3427,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3251,6 +3457,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3279,6 +3487,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3307,6 +3517,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3335,6 +3547,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3363,6 +3577,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3391,6 +3607,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3419,6 +3637,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3447,6 +3667,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3475,6 +3697,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3503,6 +3727,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3531,6 +3757,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3559,6 +3787,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3587,6 +3817,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3615,6 +3847,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3643,6 +3877,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3671,6 +3907,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3699,6 +3937,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3727,6 +3967,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3755,6 +3997,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3783,6 +4027,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3811,6 +4057,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3839,6 +4087,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3867,6 +4117,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3895,6 +4147,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3923,6 +4177,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3951,6 +4207,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3979,6 +4237,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4007,6 +4267,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -4035,6 +4297,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -4063,6 +4327,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -4091,6 +4357,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4119,6 +4387,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -4147,6 +4417,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4175,6 +4447,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -4203,6 +4477,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4231,6 +4507,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -4259,6 +4537,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4287,6 +4567,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4315,6 +4597,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4343,6 +4627,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -4371,6 +4657,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4399,6 +4687,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -4427,6 +4717,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4455,6 +4747,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4483,6 +4777,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4511,6 +4807,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4539,6 +4837,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -4567,6 +4867,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -4595,6 +4897,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4623,6 +4927,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -4651,6 +4957,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -4679,6 +4987,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -4707,6 +5017,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -4735,6 +5047,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -4763,6 +5077,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4791,6 +5107,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -4819,6 +5137,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -4847,6 +5167,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -4875,6 +5197,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -4903,6 +5227,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -4931,6 +5257,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -4959,6 +5287,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -4987,6 +5317,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -5015,6 +5347,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -5043,6 +5377,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -5071,6 +5407,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -5099,6 +5437,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -5127,6 +5467,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -5155,6 +5497,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -5183,6 +5527,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -5211,6 +5557,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -5239,6 +5587,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -5267,6 +5617,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5295,6 +5647,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -5323,6 +5677,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -5351,6 +5707,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -5379,6 +5737,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -5407,6 +5767,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -5435,6 +5797,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -5463,6 +5827,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -5491,6 +5857,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -5519,6 +5887,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -5547,6 +5917,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -5575,6 +5947,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -5603,6 +5977,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -5631,6 +6007,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -5659,6 +6037,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5687,6 +6067,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -5715,6 +6097,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -5743,6 +6127,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -5771,6 +6157,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -5799,6 +6187,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -5827,6 +6217,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -5855,6 +6247,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -5883,6 +6277,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -5911,6 +6307,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -5939,6 +6337,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -5967,6 +6367,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -5995,6 +6397,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -6023,6 +6427,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -6051,6 +6457,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -6079,6 +6487,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -6107,6 +6517,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -6135,6 +6547,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -6163,6 +6577,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -6191,6 +6607,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -6219,6 +6637,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -6247,6 +6667,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -6275,6 +6697,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -6303,6 +6727,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -6331,6 +6757,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -6359,6 +6787,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -6387,6 +6817,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -6415,6 +6847,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -6443,6 +6877,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -6471,6 +6907,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -6499,6 +6937,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -6527,6 +6967,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -6555,6 +6997,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -6583,6 +7027,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -6611,6 +7057,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -6639,6 +7087,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -6667,6 +7117,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -6695,6 +7147,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -6723,6 +7177,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -6751,6 +7207,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -6779,6 +7237,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -6807,6 +7267,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -6835,6 +7297,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -6863,6 +7327,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -6891,6 +7357,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -6919,6 +7387,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -6947,6 +7417,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -6975,6 +7447,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -7003,6 +7477,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -7031,6 +7507,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -7059,6 +7537,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -7087,6 +7567,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -7115,6 +7597,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -7143,6 +7627,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -7171,6 +7657,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -7199,6 +7687,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -7227,6 +7717,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -7255,6 +7747,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -7283,6 +7777,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -7311,6 +7807,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -7339,6 +7837,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -7367,6 +7867,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -7395,6 +7897,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -7423,6 +7927,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -7451,6 +7957,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -7479,6 +7987,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -7507,6 +8017,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -7535,6 +8047,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -7563,6 +8077,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -7591,6 +8107,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -7619,6 +8137,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -7647,6 +8167,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G256" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -7675,6 +8197,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -7703,6 +8227,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G258" s="2" t="inlineStr"/>
+      <c r="H258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -7731,6 +8257,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G259" s="2" t="inlineStr"/>
+      <c r="H259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -7759,6 +8287,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G260" s="2" t="inlineStr"/>
+      <c r="H260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -7787,6 +8317,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G261" s="2" t="inlineStr"/>
+      <c r="H261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -7815,6 +8347,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G262" s="2" t="inlineStr"/>
+      <c r="H262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -7843,6 +8377,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -7871,6 +8407,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -7899,6 +8437,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -7927,6 +8467,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -7955,6 +8497,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -7983,6 +8527,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -8011,6 +8557,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -8039,6 +8587,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -8067,6 +8617,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -8095,6 +8647,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -8123,6 +8677,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -8151,6 +8707,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -8179,6 +8737,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -8207,6 +8767,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G276" s="2" t="inlineStr"/>
+      <c r="H276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -8235,6 +8797,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G277" s="2" t="inlineStr"/>
+      <c r="H277" s="2" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -8263,6 +8827,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G278" s="2" t="inlineStr"/>
+      <c r="H278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -8291,6 +8857,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G279" s="2" t="inlineStr"/>
+      <c r="H279" s="2" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -8319,6 +8887,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G280" s="2" t="inlineStr"/>
+      <c r="H280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -8347,6 +8917,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G281" s="2" t="inlineStr"/>
+      <c r="H281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -8375,6 +8947,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G282" s="2" t="inlineStr"/>
+      <c r="H282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -8403,6 +8977,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G283" s="2" t="inlineStr"/>
+      <c r="H283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -8431,6 +9007,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -8459,6 +9037,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -8487,6 +9067,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -8515,6 +9097,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -8543,6 +9127,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -8571,6 +9157,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G289" s="2" t="inlineStr"/>
+      <c r="H289" s="2" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -8599,6 +9187,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G290" s="2" t="inlineStr"/>
+      <c r="H290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -8627,6 +9217,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G291" s="2" t="inlineStr"/>
+      <c r="H291" s="2" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -8655,6 +9247,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G292" s="2" t="inlineStr"/>
+      <c r="H292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -8683,6 +9277,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G293" s="2" t="inlineStr"/>
+      <c r="H293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -8711,6 +9307,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G294" s="2" t="inlineStr"/>
+      <c r="H294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -8739,6 +9337,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G295" s="2" t="inlineStr"/>
+      <c r="H295" s="2" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -8767,6 +9367,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G296" s="2" t="inlineStr"/>
+      <c r="H296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -8795,6 +9397,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G297" s="2" t="inlineStr"/>
+      <c r="H297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -8823,6 +9427,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G298" s="2" t="inlineStr"/>
+      <c r="H298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -8851,6 +9457,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G299" s="2" t="inlineStr"/>
+      <c r="H299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -8879,6 +9487,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G300" s="2" t="inlineStr"/>
+      <c r="H300" s="2" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -8907,6 +9517,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G301" s="2" t="inlineStr"/>
+      <c r="H301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -8935,6 +9547,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G302" s="2" t="inlineStr"/>
+      <c r="H302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -8963,6 +9577,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G303" s="2" t="inlineStr"/>
+      <c r="H303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -8991,6 +9607,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G304" s="2" t="inlineStr"/>
+      <c r="H304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -9019,6 +9637,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G305" s="2" t="inlineStr"/>
+      <c r="H305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -9047,6 +9667,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G306" s="2" t="inlineStr"/>
+      <c r="H306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -9075,6 +9697,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G307" s="2" t="inlineStr"/>
+      <c r="H307" s="2" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -9103,6 +9727,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G308" s="2" t="inlineStr"/>
+      <c r="H308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -9131,6 +9757,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G309" s="2" t="inlineStr"/>
+      <c r="H309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -9159,6 +9787,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G310" s="2" t="inlineStr"/>
+      <c r="H310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -9187,6 +9817,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G311" s="2" t="inlineStr"/>
+      <c r="H311" s="2" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -9215,6 +9847,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G312" s="2" t="inlineStr"/>
+      <c r="H312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -9243,6 +9877,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G313" s="2" t="inlineStr"/>
+      <c r="H313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -9271,6 +9907,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G314" s="2" t="inlineStr"/>
+      <c r="H314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -9299,6 +9937,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G315" s="2" t="inlineStr"/>
+      <c r="H315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -9327,6 +9967,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G316" s="2" t="inlineStr"/>
+      <c r="H316" s="2" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -9355,6 +9997,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G317" s="2" t="inlineStr"/>
+      <c r="H317" s="2" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -9383,6 +10027,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G318" s="2" t="inlineStr"/>
+      <c r="H318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -9411,6 +10057,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G319" s="2" t="inlineStr"/>
+      <c r="H319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -9439,6 +10087,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G320" s="2" t="inlineStr"/>
+      <c r="H320" s="2" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -9467,6 +10117,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G321" s="2" t="inlineStr"/>
+      <c r="H321" s="2" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -9495,6 +10147,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G322" s="2" t="inlineStr"/>
+      <c r="H322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -9523,6 +10177,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G323" s="2" t="inlineStr"/>
+      <c r="H323" s="2" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -9551,6 +10207,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G324" s="2" t="inlineStr"/>
+      <c r="H324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -9579,6 +10237,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G325" s="2" t="inlineStr"/>
+      <c r="H325" s="2" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -9607,6 +10267,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G326" s="2" t="inlineStr"/>
+      <c r="H326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -9635,6 +10297,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G327" s="2" t="inlineStr"/>
+      <c r="H327" s="2" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -9663,6 +10327,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G328" s="2" t="inlineStr"/>
+      <c r="H328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -9691,6 +10357,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G329" s="2" t="inlineStr"/>
+      <c r="H329" s="2" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -9719,6 +10387,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G330" s="2" t="inlineStr"/>
+      <c r="H330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -9747,6 +10417,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G331" s="2" t="inlineStr"/>
+      <c r="H331" s="2" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -9775,6 +10447,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G332" s="2" t="inlineStr"/>
+      <c r="H332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -9803,6 +10477,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G333" s="2" t="inlineStr"/>
+      <c r="H333" s="2" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -9831,6 +10507,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G334" s="2" t="inlineStr"/>
+      <c r="H334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -9859,6 +10537,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G335" s="2" t="inlineStr"/>
+      <c r="H335" s="2" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -9887,6 +10567,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G336" s="2" t="inlineStr"/>
+      <c r="H336" s="2" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -9915,6 +10597,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G337" s="2" t="inlineStr"/>
+      <c r="H337" s="2" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -9943,6 +10627,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G338" s="2" t="inlineStr"/>
+      <c r="H338" s="2" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -9971,6 +10657,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G339" s="2" t="inlineStr"/>
+      <c r="H339" s="2" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -9999,6 +10687,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G340" s="2" t="inlineStr"/>
+      <c r="H340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -10027,6 +10717,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G341" s="2" t="inlineStr"/>
+      <c r="H341" s="2" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -10055,6 +10747,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G342" s="2" t="inlineStr"/>
+      <c r="H342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -10083,6 +10777,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G343" s="2" t="inlineStr"/>
+      <c r="H343" s="2" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -10111,6 +10807,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G344" s="2" t="inlineStr"/>
+      <c r="H344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -10139,6 +10837,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G345" s="2" t="inlineStr"/>
+      <c r="H345" s="2" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -10167,6 +10867,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G346" s="2" t="inlineStr"/>
+      <c r="H346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -10195,6 +10897,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G347" s="2" t="inlineStr"/>
+      <c r="H347" s="2" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -10223,6 +10927,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G348" s="2" t="inlineStr"/>
+      <c r="H348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -10251,6 +10957,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G349" s="2" t="inlineStr"/>
+      <c r="H349" s="2" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -10279,6 +10987,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G350" s="2" t="inlineStr"/>
+      <c r="H350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -10307,6 +11017,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G351" s="2" t="inlineStr"/>
+      <c r="H351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -10335,6 +11047,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G352" s="2" t="inlineStr"/>
+      <c r="H352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -10363,6 +11077,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G353" s="2" t="inlineStr"/>
+      <c r="H353" s="2" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -10391,6 +11107,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G354" s="2" t="inlineStr"/>
+      <c r="H354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -10419,6 +11137,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G355" s="2" t="inlineStr"/>
+      <c r="H355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -10447,6 +11167,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G356" s="2" t="inlineStr"/>
+      <c r="H356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -10475,6 +11197,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G357" s="2" t="inlineStr"/>
+      <c r="H357" s="2" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -10503,6 +11227,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G358" s="2" t="inlineStr"/>
+      <c r="H358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -10531,6 +11257,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G359" s="2" t="inlineStr"/>
+      <c r="H359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -10559,6 +11287,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G360" s="2" t="inlineStr"/>
+      <c r="H360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -10587,6 +11317,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G361" s="2" t="inlineStr"/>
+      <c r="H361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -10615,6 +11347,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G362" s="2" t="inlineStr"/>
+      <c r="H362" s="2" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -10643,6 +11377,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G363" s="2" t="inlineStr"/>
+      <c r="H363" s="2" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -10671,6 +11407,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G364" s="2" t="inlineStr"/>
+      <c r="H364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -10699,6 +11437,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G365" s="2" t="inlineStr"/>
+      <c r="H365" s="2" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -10727,6 +11467,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G366" s="2" t="inlineStr"/>
+      <c r="H366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -10755,6 +11497,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G367" s="2" t="inlineStr"/>
+      <c r="H367" s="2" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -10783,6 +11527,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G368" s="2" t="inlineStr"/>
+      <c r="H368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -10811,6 +11557,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G369" s="2" t="inlineStr"/>
+      <c r="H369" s="2" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -10839,6 +11587,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G370" s="2" t="inlineStr"/>
+      <c r="H370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -10867,6 +11617,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G371" s="2" t="inlineStr"/>
+      <c r="H371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -10895,6 +11647,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G372" s="2" t="inlineStr"/>
+      <c r="H372" s="2" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -10923,6 +11677,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G373" s="2" t="inlineStr"/>
+      <c r="H373" s="2" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -10951,6 +11707,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G374" s="2" t="inlineStr"/>
+      <c r="H374" s="2" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -10979,6 +11737,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G375" s="2" t="inlineStr"/>
+      <c r="H375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -11007,6 +11767,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G376" s="2" t="inlineStr"/>
+      <c r="H376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -11035,6 +11797,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G377" s="2" t="inlineStr"/>
+      <c r="H377" s="2" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -11063,6 +11827,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G378" s="2" t="inlineStr"/>
+      <c r="H378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -11091,6 +11857,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G379" s="2" t="inlineStr"/>
+      <c r="H379" s="2" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -11119,6 +11887,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G380" s="2" t="inlineStr"/>
+      <c r="H380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -11147,6 +11917,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G381" s="2" t="inlineStr"/>
+      <c r="H381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -11175,6 +11947,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G382" s="2" t="inlineStr"/>
+      <c r="H382" s="2" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -11203,6 +11977,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G383" s="2" t="inlineStr"/>
+      <c r="H383" s="2" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -11231,6 +12007,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G384" s="2" t="inlineStr"/>
+      <c r="H384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -11259,6 +12037,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G385" s="2" t="inlineStr"/>
+      <c r="H385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -11287,6 +12067,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G386" s="2" t="inlineStr"/>
+      <c r="H386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -11315,6 +12097,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G387" s="2" t="inlineStr"/>
+      <c r="H387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -11343,6 +12127,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G388" s="2" t="inlineStr"/>
+      <c r="H388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -11371,6 +12157,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G389" s="2" t="inlineStr"/>
+      <c r="H389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -11399,6 +12187,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G390" s="2" t="inlineStr"/>
+      <c r="H390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -11427,6 +12217,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G391" s="2" t="inlineStr"/>
+      <c r="H391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -11455,6 +12247,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G392" s="2" t="inlineStr"/>
+      <c r="H392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -11483,6 +12277,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G393" s="2" t="inlineStr"/>
+      <c r="H393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -11511,6 +12307,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G394" s="2" t="inlineStr"/>
+      <c r="H394" s="2" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -11539,6 +12337,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G395" s="2" t="inlineStr"/>
+      <c r="H395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -11567,6 +12367,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G396" s="2" t="inlineStr"/>
+      <c r="H396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -11595,6 +12397,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G397" s="2" t="inlineStr"/>
+      <c r="H397" s="2" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -11623,6 +12427,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G398" s="2" t="inlineStr"/>
+      <c r="H398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -11651,6 +12457,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G399" s="2" t="inlineStr"/>
+      <c r="H399" s="2" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -11679,6 +12487,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G400" s="2" t="inlineStr"/>
+      <c r="H400" s="2" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -11707,6 +12517,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G401" s="2" t="inlineStr"/>
+      <c r="H401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -11735,6 +12547,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G402" s="2" t="inlineStr"/>
+      <c r="H402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -11763,6 +12577,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G403" s="2" t="inlineStr"/>
+      <c r="H403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -11791,6 +12607,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G404" s="2" t="inlineStr"/>
+      <c r="H404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -11819,6 +12637,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G405" s="2" t="inlineStr"/>
+      <c r="H405" s="2" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -11847,6 +12667,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G406" s="2" t="inlineStr"/>
+      <c r="H406" s="2" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -11875,6 +12697,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G407" s="2" t="inlineStr"/>
+      <c r="H407" s="2" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -11903,6 +12727,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G408" s="2" t="inlineStr"/>
+      <c r="H408" s="2" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -11931,6 +12757,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G409" s="2" t="inlineStr"/>
+      <c r="H409" s="2" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -11959,6 +12787,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G410" s="2" t="inlineStr"/>
+      <c r="H410" s="2" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -11987,6 +12817,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G411" s="2" t="inlineStr"/>
+      <c r="H411" s="2" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -12015,6 +12847,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G412" s="2" t="inlineStr"/>
+      <c r="H412" s="2" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -12043,6 +12877,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G413" s="2" t="inlineStr"/>
+      <c r="H413" s="2" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -12071,6 +12907,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G414" s="2" t="inlineStr"/>
+      <c r="H414" s="2" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -12099,6 +12937,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G415" s="2" t="inlineStr"/>
+      <c r="H415" s="2" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -12127,6 +12967,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G416" s="2" t="inlineStr"/>
+      <c r="H416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -12155,6 +12997,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G417" s="2" t="inlineStr"/>
+      <c r="H417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -12183,6 +13027,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G418" s="2" t="inlineStr"/>
+      <c r="H418" s="2" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -12211,6 +13057,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G419" s="2" t="inlineStr"/>
+      <c r="H419" s="2" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -12239,6 +13087,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G420" s="2" t="inlineStr"/>
+      <c r="H420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -12267,6 +13117,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G421" s="2" t="inlineStr"/>
+      <c r="H421" s="2" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -12295,6 +13147,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G422" s="2" t="inlineStr"/>
+      <c r="H422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -12323,6 +13177,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G423" s="2" t="inlineStr"/>
+      <c r="H423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -12351,6 +13207,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G424" s="2" t="inlineStr"/>
+      <c r="H424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -12379,6 +13237,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G425" s="2" t="inlineStr"/>
+      <c r="H425" s="2" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -12407,6 +13267,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G426" s="2" t="inlineStr"/>
+      <c r="H426" s="2" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -12435,6 +13297,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G427" s="2" t="inlineStr"/>
+      <c r="H427" s="2" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -12463,6 +13327,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G428" s="2" t="inlineStr"/>
+      <c r="H428" s="2" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -12491,6 +13357,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G429" s="2" t="inlineStr"/>
+      <c r="H429" s="2" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -12519,6 +13387,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G430" s="2" t="inlineStr"/>
+      <c r="H430" s="2" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -12547,6 +13417,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G431" s="2" t="inlineStr"/>
+      <c r="H431" s="2" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -12575,6 +13447,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G432" s="2" t="inlineStr"/>
+      <c r="H432" s="2" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -12603,6 +13477,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G433" s="2" t="inlineStr"/>
+      <c r="H433" s="2" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -12631,6 +13507,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G434" s="2" t="inlineStr"/>
+      <c r="H434" s="2" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -12659,6 +13537,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G435" s="2" t="inlineStr"/>
+      <c r="H435" s="2" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -12687,6 +13567,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G436" s="2" t="inlineStr"/>
+      <c r="H436" s="2" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -12715,6 +13597,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G437" s="2" t="inlineStr"/>
+      <c r="H437" s="2" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -12743,6 +13627,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G438" s="2" t="inlineStr"/>
+      <c r="H438" s="2" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -12771,6 +13657,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G439" s="2" t="inlineStr"/>
+      <c r="H439" s="2" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -12799,6 +13687,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G440" s="2" t="inlineStr"/>
+      <c r="H440" s="2" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -12827,6 +13717,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G441" s="2" t="inlineStr"/>
+      <c r="H441" s="2" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -12855,6 +13747,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G442" s="2" t="inlineStr"/>
+      <c r="H442" s="2" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -12883,6 +13777,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G443" s="2" t="inlineStr"/>
+      <c r="H443" s="2" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -12911,6 +13807,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G444" s="2" t="inlineStr"/>
+      <c r="H444" s="2" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -12939,6 +13837,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G445" s="2" t="inlineStr"/>
+      <c r="H445" s="2" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -12967,6 +13867,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G446" s="2" t="inlineStr"/>
+      <c r="H446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -12995,6 +13897,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G447" s="2" t="inlineStr"/>
+      <c r="H447" s="2" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -13023,6 +13927,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G448" s="2" t="inlineStr"/>
+      <c r="H448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -13051,6 +13957,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G449" s="2" t="inlineStr"/>
+      <c r="H449" s="2" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -13079,6 +13987,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G450" s="2" t="inlineStr"/>
+      <c r="H450" s="2" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -13107,6 +14017,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G451" s="2" t="inlineStr"/>
+      <c r="H451" s="2" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -13135,6 +14047,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G452" s="2" t="inlineStr"/>
+      <c r="H452" s="2" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -13163,6 +14077,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G453" s="2" t="inlineStr"/>
+      <c r="H453" s="2" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -13191,6 +14107,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G454" s="2" t="inlineStr"/>
+      <c r="H454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -13219,6 +14137,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G455" s="2" t="inlineStr"/>
+      <c r="H455" s="2" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -13247,6 +14167,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G456" s="2" t="inlineStr"/>
+      <c r="H456" s="2" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -13275,6 +14197,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G457" s="2" t="inlineStr"/>
+      <c r="H457" s="2" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -13303,6 +14227,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G458" s="2" t="inlineStr"/>
+      <c r="H458" s="2" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -13331,6 +14257,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G459" s="2" t="inlineStr"/>
+      <c r="H459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -13359,6 +14287,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G460" s="2" t="inlineStr"/>
+      <c r="H460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -13387,6 +14317,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G461" s="2" t="inlineStr"/>
+      <c r="H461" s="2" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -13415,6 +14347,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G462" s="2" t="inlineStr"/>
+      <c r="H462" s="2" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -13443,6 +14377,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G463" s="2" t="inlineStr"/>
+      <c r="H463" s="2" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -13471,6 +14407,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G464" s="2" t="inlineStr"/>
+      <c r="H464" s="2" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -13499,6 +14437,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G465" s="2" t="inlineStr"/>
+      <c r="H465" s="2" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -13527,6 +14467,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G466" s="2" t="inlineStr"/>
+      <c r="H466" s="2" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -13555,6 +14497,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G467" s="2" t="inlineStr"/>
+      <c r="H467" s="2" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -13583,6 +14527,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G468" s="2" t="inlineStr"/>
+      <c r="H468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -13611,6 +14557,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G469" s="2" t="inlineStr"/>
+      <c r="H469" s="2" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -13639,6 +14587,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G470" s="2" t="inlineStr"/>
+      <c r="H470" s="2" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -13667,6 +14617,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G471" s="2" t="inlineStr"/>
+      <c r="H471" s="2" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -13695,6 +14647,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G472" s="2" t="inlineStr"/>
+      <c r="H472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -13723,6 +14677,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G473" s="2" t="inlineStr"/>
+      <c r="H473" s="2" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -13751,6 +14707,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G474" s="2" t="inlineStr"/>
+      <c r="H474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -13779,6 +14737,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G475" s="2" t="inlineStr"/>
+      <c r="H475" s="2" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -13807,6 +14767,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G476" s="2" t="inlineStr"/>
+      <c r="H476" s="2" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -13835,6 +14797,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G477" s="2" t="inlineStr"/>
+      <c r="H477" s="2" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -13863,6 +14827,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G478" s="2" t="inlineStr"/>
+      <c r="H478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -13891,6 +14857,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G479" s="2" t="inlineStr"/>
+      <c r="H479" s="2" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -13919,6 +14887,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G480" s="2" t="inlineStr"/>
+      <c r="H480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -13947,6 +14917,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G481" s="2" t="inlineStr"/>
+      <c r="H481" s="2" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -13975,6 +14947,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G482" s="2" t="inlineStr"/>
+      <c r="H482" s="2" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -14003,6 +14977,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G483" s="2" t="inlineStr"/>
+      <c r="H483" s="2" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -14031,6 +15007,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G484" s="2" t="inlineStr"/>
+      <c r="H484" s="2" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -14059,6 +15037,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G485" s="2" t="inlineStr"/>
+      <c r="H485" s="2" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -14087,6 +15067,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G486" s="2" t="inlineStr"/>
+      <c r="H486" s="2" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -14115,6 +15097,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G487" s="2" t="inlineStr"/>
+      <c r="H487" s="2" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -14143,6 +15127,8 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G488" s="2" t="inlineStr"/>
+      <c r="H488" s="2" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -14171,11 +15157,16 @@
           <t>ALTA</t>
         </is>
       </c>
+      <c r="G489" s="2" t="inlineStr"/>
+      <c r="H489" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F2:F489" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estatus inválido" error="Elige ALTA o BAJA." type="list">
       <formula1>"ALTA,BAJA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H489" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo de empleado inválido" error="Elige ADMINISTRATIVO, OPERATIVO o SINDICALIZADO." type="list">
+      <formula1>"ADMINISTRATIVO,OPERATIVO,SINDICALIZADO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14188,7 +15179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -14231,7 +15222,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>2. Corrige o completa las columnas Fecha_Ingreso, Fecha_Baja y Estatus (columna F tiene lista desplegable ALTA/BAJA).</t>
+          <t>2. Corrige o completa las columnas Fecha_Ingreso, Fecha_Baja, Estatus, Fecha_Nacimiento y Tipo_Empleado (columnas F y H tienen lista desplegable).</t>
         </is>
       </c>
     </row>
@@ -14276,26 +15267,40 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>• Actualiza la fecha de ingreso, fecha de baja y estatus de cada empleado que exista en el directorio.</t>
+          <t>• Actualiza la fecha de ingreso, fecha de baja, estatus, fecha de nacimiento y tipo de empleado de cada empleado que exista en el directorio.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>• Si un número de empleado no existe en el directorio, esa fila se marca como error y no se sube (las demás filas correctas sí se guardan).</t>
+          <t>• Fecha_Nacimiento y Tipo_Empleado alimentan el "Dashboard Cumpleañeros" — sin esta información, un empleado no aparecerá ahí.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>• Si Estatus tiene un valor distinto de ALTA o BAJA, esa fila se marca como error y se conserva el estatus que ya tenía.</t>
+          <t>• Tipo_Empleado debe ser ADMINISTRATIVO, OPERATIVO o SINDICALIZADO. Los empleados ADMINISTRATIVOS generan una alerta especial en el Dashboard Cumpleañeros el mes de su cumpleaños.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>• Si un número de empleado no existe en el directorio, esa fila se marca como error y no se sube (las demás filas correctas sí se guardan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>• Si Estatus o Tipo_Empleado tienen un valor inválido, esa fila se marca como error para ese campo y se conserva el valor anterior — el resto de la fila sí se actualiza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>• Puedes subir esta plantilla las veces que quieras — cada vez reemplaza los datos de los empleados que incluyas.</t>
         </is>
